--- a/Result/profitability/6234.xlsx
+++ b/Result/profitability/6234.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.42</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01500000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="N2" t="n">
-        <v>10.6525</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08125</v>
+        <v>0.065</v>
       </c>
       <c r="N3" t="n">
-        <v>11.31375</v>
+        <v>10.945</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05749999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>11.00625</v>
+        <v>10.9625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.025</v>
+        <v>0.14375</v>
       </c>
       <c r="N5" t="n">
-        <v>11.285</v>
+        <v>11.655</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.12875</v>
+        <v>0.10375</v>
       </c>
       <c r="N6" t="n">
-        <v>11.3375</v>
+        <v>12.31625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.22</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.06</v>
+        <v>-0.10125</v>
       </c>
       <c r="N7" t="n">
-        <v>9.352500000000001</v>
+        <v>9.73625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-2.13</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.37875</v>
+        <v>-0.39625</v>
       </c>
       <c r="N8" t="n">
-        <v>1.805000000000001</v>
+        <v>2.003749999999999</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>-0.5974999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8012499999999998</v>
+        <v>-0.8012500000000002</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>-0.5599999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.482499999999999</v>
+        <v>-3.4825</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.61625</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.282499999999999</v>
+        <v>-4.282500000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>-0.61125</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.417499999999999</v>
+        <v>-2.4175</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6234</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>148</v>
+      </c>
+      <c r="D75" t="n">
+        <v>135</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>11</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.07875000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.373749999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6086956521739131</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2214484679665738</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.104651162790698</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.5094664371772806</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
